--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486665_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486665_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2356</v>
+        <v>4.7529</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1883</v>
+        <v>4.8298</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0472</v>
+        <v>-0.0769</v>
       </c>
       <c r="G2" t="n">
         <v>4.0084</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2964</v>
+        <v>0.8138</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8547</v>
+        <v>0.4962</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4418</v>
+        <v>0.3176</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2277</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8951</v>
+        <v>3.767</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4921</v>
+        <v>0.8855</v>
       </c>
       <c r="F3" t="n">
-        <v>3.403</v>
+        <v>2.8815</v>
       </c>
       <c r="G3" t="n">
         <v>2.1416</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7695</v>
+        <v>1.6414</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0752</v>
+        <v>0.4685</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6943</v>
+        <v>1.1729</v>
       </c>
       <c r="V3" t="n">
         <v>1.1424</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0044</v>
+        <v>3.4359</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0582</v>
+        <v>2.8373</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9462</v>
+        <v>0.5986</v>
       </c>
       <c r="G4" t="n">
         <v>6.42</v>
@@ -766,13 +766,13 @@
         <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2376</v>
+        <v>0.6691</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1036</v>
+        <v>-0.3245</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3412</v>
+        <v>0.9936</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3709</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.405</v>
+        <v>2.7346</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9285</v>
+        <v>0.9758</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4765</v>
+        <v>1.7588</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2797</v>
+        <v>0.1605</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0484</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7687</v>
+        <v>0.1605</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7287</v>
+        <v>0.4031</v>
       </c>
       <c r="K5" t="n">
-        <v>1.566</v>
+        <v>-0.4131</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1628</v>
+        <v>0.8161</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.449</v>
+        <v>-0.2426</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4824</v>
+        <v>0.4131</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9314</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5792</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5446</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5461</v>
+        <v>0.393</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1652</v>
+        <v>-0.2141</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3809</v>
+        <v>0.6072</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3.7257</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.6831</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4533</v>
+        <v>2.645</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1415</v>
+        <v>1.0941</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3118</v>
+        <v>1.551</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1605</v>
+        <v>1.2797</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>2.0484</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1605</v>
+        <v>-0.7687</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4031</v>
+        <v>1.7287</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4131</v>
+        <v>1.566</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8161</v>
+        <v>0.1628</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2426</v>
+        <v>-0.449</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4131</v>
+        <v>0.4824</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.9314</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8883</v>
+        <v>0.7861</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0485</v>
+        <v>0.3307</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1602</v>
+        <v>0.4554</v>
       </c>
       <c r="V6" t="n">
-        <v>3.7257</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.6831</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.0896</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6206</v>
+        <v>-0.462</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5268</v>
+        <v>0.5516</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4413</v>
@@ -1000,13 +1000,13 @@
         <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0386</v>
+        <v>0.1448</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0275</v>
+        <v>0.1861</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0413</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5208</v>
+        <v>0.0806</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4566</v>
+        <v>-0.029</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.1096</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4712</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0497</v>
+        <v>0.5517</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4966</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.447</v>
+        <v>0.6208</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>M. LORENZO SALCEDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9205</v>
+        <v>-1.4143</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6505</v>
+        <v>-2.1932</v>
       </c>
       <c r="F9" t="n">
-        <v>0.73</v>
+        <v>0.7789</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6804</v>
+        <v>-0.18</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8544</v>
+        <v>0.1862</v>
       </c>
       <c r="I9" t="n">
-        <v>0.174</v>
+        <v>-0.3662</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.224</v>
+        <v>-0.3243</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.5088</v>
+        <v>0.3244</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2848</v>
+        <v>-0.6488</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4564</v>
+        <v>0.1443</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3456</v>
+        <v>-0.1382</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1108</v>
+        <v>0.2826</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1931</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>1.71</v>
+        <v>0.3103</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2959</v>
+        <v>0.0619</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4141</v>
+        <v>0.2484</v>
       </c>
       <c r="V9" t="n">
-        <v>0.243</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.243</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LORENZO SALCEDA</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6749</v>
+        <v>-1.7754</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5035</v>
+        <v>-2.6295</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8286</v>
+        <v>0.8541</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.18</v>
+        <v>-2.6804</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1862</v>
+        <v>-2.8544</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3662</v>
+        <v>0.174</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3243</v>
+        <v>-2.224</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3244</v>
+        <v>-2.5088</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6488</v>
+        <v>0.2848</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1443</v>
+        <v>-0.4564</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1382</v>
+        <v>-0.3456</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2826</v>
+        <v>-0.1108</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5446</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0497</v>
+        <v>0.8551</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2484</v>
+        <v>0.3169</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2981</v>
+        <v>0.5383</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7403</v>
+        <v>-2.5086</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7288</v>
+        <v>-2.522</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0115</v>
+        <v>0.0133</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6428</v>
@@ -1312,13 +1312,13 @@
         <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.1655</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0828</v>
+        <v>0.124</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0167</v>
+        <v>0.0415</v>
       </c>
       <c r="V11" t="n">
         <v>0.2856</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.573</v>
+        <v>-5.2337</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8023</v>
+        <v>-3.6367</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7708</v>
+        <v>-1.597</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4238</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>0.364</v>
+        <v>0.7034</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0279</v>
+        <v>0.1377</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3919</v>
+        <v>0.5657</v>
       </c>
       <c r="V12" t="n">
         <v>-2.741</v>
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4701</v>
+        <v>6.573600000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9537</v>
+        <v>-0.8498999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>7.4236</v>
+        <v>7.423500000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>7.170700000000002</v>
+        <v>7.1707</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3435999999999999</v>
+        <v>0.3435999999999997</v>
       </c>
       <c r="I13" t="n">
-        <v>6.827100000000002</v>
+        <v>6.8271</v>
       </c>
       <c r="J13" t="n">
         <v>11.6981</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3404999999999997</v>
+        <v>-0.3404999999999999</v>
       </c>
       <c r="L13" t="n">
         <v>12.0384</v>
@@ -1453,10 +1453,10 @@
         <v>-4.5274</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6839999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.2114</v>
+        <v>-5.211399999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-8.6884</v>
@@ -1468,13 +1468,13 @@
         <v>11.5847</v>
       </c>
       <c r="S13" t="n">
-        <v>5.930499999999999</v>
+        <v>7.0342</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4107000000000003</v>
+        <v>1.5143</v>
       </c>
       <c r="U13" t="n">
-        <v>5.52</v>
+        <v>5.5201</v>
       </c>
       <c r="V13" t="n">
         <v>1.0571</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5267</v>
+        <v>3.7625</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8557</v>
+        <v>2.1659</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6711</v>
+        <v>1.5966</v>
       </c>
       <c r="G14" t="n">
         <v>4.1378</v>
@@ -1546,13 +1546,13 @@
         <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5185</v>
+        <v>-0.2828</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.607</v>
+        <v>-0.2967</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0885</v>
+        <v>0.014</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2856</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7155</v>
+        <v>0.3432</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2743</v>
+        <v>2.6537</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5588</v>
+        <v>-2.3105</v>
       </c>
       <c r="G15" t="n">
         <v>0.1426</v>
@@ -1624,13 +1624,13 @@
         <v>2.8962</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5244</v>
+        <v>-0.8966</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.111</v>
+        <v>-0.7315</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4135</v>
+        <v>-0.1651</v>
       </c>
       <c r="V15" t="n">
         <v>-1.7989</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3999</v>
+        <v>0.1654</v>
       </c>
       <c r="E16" t="n">
         <v>-1.3863</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7863</v>
+        <v>1.5517</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5132</v>
@@ -1702,13 +1702,13 @@
         <v>3.2823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4963</v>
+        <v>-0.7309</v>
       </c>
       <c r="T16" t="n">
         <v>-0.966</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4696</v>
+        <v>0.2351</v>
       </c>
       <c r="V16" t="n">
         <v>0.2856</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4838</v>
+        <v>-0.3666</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2273</v>
+        <v>1.3308</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7111</v>
+        <v>-1.6973</v>
       </c>
       <c r="G17" t="n">
         <v>0.1717</v>
@@ -1780,13 +1780,13 @@
         <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7447</v>
+        <v>-0.6276</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7725</v>
+        <v>-0.6691</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0278</v>
+        <v>0.0416</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8415</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. BUENO CASTILLO</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4657</v>
+        <v>-0.8413</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4294</v>
+        <v>-2.6276</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8951</v>
+        <v>1.7864</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1094</v>
+        <v>-3.8978</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1991</v>
+        <v>-0.6899</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0896</v>
+        <v>-3.2078</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3126</v>
+        <v>-2.5034</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.7846</v>
+        <v>-1.172</v>
       </c>
       <c r="L18" t="n">
-        <v>3.0972</v>
+        <v>-1.3314</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.422</v>
+        <v>-1.3943</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4145</v>
+        <v>0.4821</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.0075</v>
+        <v>-1.8764</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3169</v>
+        <v>2.7031</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2524</v>
+        <v>-0.9861</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6901</v>
+        <v>-0.8073</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5623</v>
+        <v>-0.1789</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2277</v>
+        <v>2.498</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LOPEZ ROMERA</t>
+          <t>L. BUENO CASTILLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6084</v>
+        <v>-1.2615</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2412</v>
+        <v>0.2226</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6328</v>
+        <v>-1.484</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8691</v>
+        <v>-1.1094</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1864</v>
+        <v>-2.1991</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6827</v>
+        <v>1.0896</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6688</v>
+        <v>1.3126</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0207</v>
+        <v>-1.7846</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6895</v>
+        <v>3.0972</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2003</v>
+        <v>-2.422</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2071</v>
+        <v>-0.4145</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0068</v>
+        <v>-2.0075</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1585</v>
+        <v>2.1239</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9308</v>
+        <v>-0.1931</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7723</v>
+        <v>2.3169</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4192</v>
+        <v>-1.0482</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3584</v>
+        <v>-0.8969</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0608</v>
+        <v>-0.1513</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7772</v>
+        <v>-1.9703</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2013</v>
+        <v>-2.4082</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4241</v>
+        <v>0.4378</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9606</v>
@@ -2014,13 +2014,13 @@
         <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0828</v>
+        <v>-0.1103</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.2899</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1658</v>
+        <v>0.1796</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2856</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>A. LOPEZ ROMERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8191</v>
+        <v>-2.0965</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1447</v>
+        <v>-2.6549</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3257</v>
+        <v>0.5583</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8978</v>
+        <v>-0.8691</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6899</v>
+        <v>-0.1864</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.2078</v>
+        <v>-0.6827</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5034</v>
+        <v>-0.6688</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.172</v>
+        <v>0.0207</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3314</v>
+        <v>-0.6895</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3943</v>
+        <v>-0.2003</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4821</v>
+        <v>-0.2071</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8764</v>
+        <v>0.0068</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5446</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1585</v>
+        <v>-1.9308</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7031</v>
+        <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9639</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3244</v>
+        <v>-0.0553</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.0137</v>
       </c>
       <c r="V21" t="n">
-        <v>2.498</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.958</v>
+        <v>-2.5154</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.2367</v>
+        <v>-4.7196</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2787</v>
+        <v>2.2042</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2728</v>
@@ -2170,13 +2170,13 @@
         <v>2.7031</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9322</v>
+        <v>-0.4896</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3244</v>
+        <v>-0.8073</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3921</v>
+        <v>0.3177</v>
       </c>
       <c r="V22" t="n">
         <v>1.5985</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4701</v>
+        <v>-4.7805</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.4235</v>
+        <v>-7.4236</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9537</v>
+        <v>2.6432</v>
       </c>
       <c r="G23" t="n">
         <v>-7.1708</v>
@@ -2224,7 +2224,7 @@
         <v>4.5274</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6839999999999995</v>
+        <v>-0.6840000000000004</v>
       </c>
       <c r="L23" t="n">
         <v>5.211400000000001</v>
@@ -2233,7 +2233,7 @@
         <v>-11.6981</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3404000000000001</v>
+        <v>0.3404</v>
       </c>
       <c r="O23" t="n">
         <v>-12.0383</v>
@@ -2248,13 +2248,13 @@
         <v>20.2732</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.9304</v>
+        <v>-5.2411</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.5201</v>
+        <v>-5.52</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4107999999999999</v>
+        <v>0.279</v>
       </c>
       <c r="V23" t="n">
         <v>-1.057199999999999</v>
